--- a/cuadros/MAYO/GUACARA.xlsx
+++ b/cuadros/MAYO/GUACARA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>SUCURSAL</t>
   </si>
@@ -55,13 +55,16 @@
     <t>ID</t>
   </si>
   <si>
+    <t>FOTO_INCIDENCIA</t>
+  </si>
+  <si>
     <t>GUACARA</t>
   </si>
   <si>
     <t>INVERSIONES LA PATRONA 2024, C.A</t>
   </si>
   <si>
-    <t>000654</t>
+    <t>654</t>
   </si>
   <si>
     <t>2026-05-01</t>
@@ -82,7 +85,7 @@
     <t>FALTANTE DE 3KG DE PATILLA</t>
   </si>
   <si>
-    <t>SIN_FOTO</t>
+    <t>5379.jpeg</t>
   </si>
   <si>
     <t>COBRO</t>
@@ -420,10 +423,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -463,46 +466,49 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="K2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/GUACARA.xlsx
+++ b/cuadros/MAYO/GUACARA.xlsx
@@ -1,118 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
-  <si>
-    <t>SUCURSAL</t>
-  </si>
-  <si>
-    <t>PROVEEDOR</t>
-  </si>
-  <si>
-    <t>FACTURA</t>
-  </si>
-  <si>
-    <t>FECHA</t>
-  </si>
-  <si>
-    <t>TIPO FISCALIZACIÓN</t>
-  </si>
-  <si>
-    <t>RESPONSABLE</t>
-  </si>
-  <si>
-    <t>INCIDENCIA</t>
-  </si>
-  <si>
-    <t>TIPO DE ERROR</t>
-  </si>
-  <si>
-    <t>OBSERVACIÓN</t>
-  </si>
-  <si>
-    <t>MONTO $</t>
-  </si>
-  <si>
-    <t>F COBRADA</t>
-  </si>
-  <si>
-    <t>CLASIFICACIÓN MONTO</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>FOTO_INCIDENCIA</t>
-  </si>
-  <si>
-    <t>GUACARA</t>
-  </si>
-  <si>
-    <t>INVERSIONES LA PATRONA 2024, C.A</t>
-  </si>
-  <si>
-    <t>654</t>
-  </si>
-  <si>
-    <t>2026-05-01</t>
-  </si>
-  <si>
-    <t>RECEPCION</t>
-  </si>
-  <si>
-    <t>GABRIELA VIVAS</t>
-  </si>
-  <si>
-    <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
-  </si>
-  <si>
-    <t>TIPO D</t>
-  </si>
-  <si>
-    <t>FALTANTE DE 3KG DE PATILLA</t>
-  </si>
-  <si>
-    <t>5379.jpeg</t>
-  </si>
-  <si>
-    <t>COBRO</t>
-  </si>
-  <si>
-    <t>HIST_20260504164252</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -127,19 +57,88 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -181,7 +180,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -213,9 +212,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -247,6 +264,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -422,93 +457,278 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
+  <cols>
+    <col width="32.3046875" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>SUCURSAL</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>FACTURA</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>FECHA</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>TIPO FISCALIZACIÓN</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>RESPONSABLE</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>INCIDENCIA</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>TIPO DE ERROR</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>OBSERVACIÓN</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>MONTO $</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>F COBRADA</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>CLASIFICACIÓN MONTO</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>FOTO_INCIDENCIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>GUACARA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>INVERSIONES LA PATRONA 2024, C.A</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>654</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>GABRIELA VIVAS</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>FALTANTE DE 3KG DE PATILLA</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>5379.jpeg</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>COBRO</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>HIST_20260504164252</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GUACARA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LA CARIDAD C.A.</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>41793</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Robert A. Nuñez</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>diferencia de pesaje por error de tara se colocaron a 2.6kg y las cestas eran 2.3kg, diferencia de 4.6 kg de pollo fresco</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>RECUPERACIÓN</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>ID_20260505165638</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>GUACARA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PASTAS CAPRI, C.A.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>420386</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>YUSBELIS CASTILLO</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>SE CARGO AL SISTEMA LA FACTURA DE OTRO PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2">
-        <v>1.69</v>
-      </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" t="s">
-        <v>25</v>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>ID_20260506083658</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/cuadros/MAYO/GUACARA.xlsx
+++ b/cuadros/MAYO/GUACARA.xlsx
@@ -2,8 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -25,24 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -57,13 +46,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -138,7 +125,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -180,7 +167,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -212,27 +199,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -264,24 +233,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -462,11 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6"/>
-  <cols>
-    <col width="32.3046875" customWidth="1" min="12" max="12"/>
-  </cols>
+  <dimension ref="A1:N5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -584,7 +532,7 @@
           <t>FALTANTE DE 3KG DE PATILLA</t>
         </is>
       </c>
-      <c r="J2" s="1" t="n">
+      <c r="J2" t="n">
         <v>1.69</v>
       </c>
       <c r="K2" t="inlineStr">
@@ -602,6 +550,7 @@
           <t>HIST_20260504164252</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -647,7 +596,7 @@
           <t>diferencia de pesaje por error de tara se colocaron a 2.6kg y las cestas eran 2.3kg, diferencia de 4.6 kg de pollo fresco</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n">
+      <c r="J3" t="n">
         <v>13.57</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -665,6 +614,7 @@
           <t>ID_20260505165638</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -677,10 +627,8 @@
           <t>PASTAS CAPRI, C.A.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>420386</t>
-        </is>
+      <c r="C4" t="n">
+        <v>420386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -730,8 +678,75 @@
           <t>ID_20260506083658</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GUACARA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>000904</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Yusbelis C. Montilla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ERROR DE KG EN TARA.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>TIPO C</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>en el melon se cargaron 2 cestas de mas</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>ID_20260508090145</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/cuadros/MAYO/GUACARA.xlsx
+++ b/cuadros/MAYO/GUACARA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -691,10 +691,8 @@
           <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>000904</t>
-        </is>
+      <c r="C5" t="n">
+        <v>904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -745,6 +743,72 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GUACARA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>RUBROS SANARE C2, C.A.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0002356</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gabriela A. Vivas</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>TIPO D</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>se cargaron 300gr de mas en el pimenton en sistema eva</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>00091910.jpeg</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>COBRO</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>ID_20260508113803</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/GUACARA.xlsx
+++ b/cuadros/MAYO/GUACARA.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -755,10 +755,8 @@
           <t>RUBROS SANARE C2, C.A.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0002356</t>
-        </is>
+      <c r="C6" t="n">
+        <v>2356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -809,6 +807,136 @@
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GUACARA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PROCESADORA DE VEGETALES Y FRUTAS PROVEFRU, C.A.</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>20496</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ELIANNYS VILLEGAS</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>TIPO B</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>SE CARGO LA FACTURA EQUIVOCADA</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>ID_20260511071755</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>GUACARA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>INVERSIONES LAS PATRONAS 2024, C.A.</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RECEPCION</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NIXILETH V. ARRIZGA</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>TIPO A</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>NUMERO DE CONTROL ,Y FACTURRA EQUIVOCADOS</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>SIN_FOTO</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NINGUNA</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ID_20260511074546</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/GUACARA.xlsx
+++ b/cuadros/MAYO/GUACARA.xlsx
@@ -26,12 +26,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor rgb="FF92D050"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +58,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -532,7 +546,7 @@
           <t>FALTANTE DE 3KG DE PATILLA</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="1" t="n">
         <v>1.69</v>
       </c>
       <c r="K2" t="inlineStr">
@@ -550,7 +564,6 @@
           <t>HIST_20260504164252</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -596,7 +609,7 @@
           <t>diferencia de pesaje por error de tara se colocaron a 2.6kg y las cestas eran 2.3kg, diferencia de 4.6 kg de pollo fresco</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="2" t="n">
         <v>13.57</v>
       </c>
       <c r="K3" t="inlineStr">
@@ -614,7 +627,6 @@
           <t>ID_20260505165638</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -678,7 +690,6 @@
           <t>ID_20260506083658</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -742,7 +753,6 @@
           <t>ID_20260508090145</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -788,7 +798,7 @@
           <t>se cargaron 300gr de mas en el pimenton en sistema eva</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" s="1" t="n">
         <v>1.37</v>
       </c>
       <c r="K6" t="inlineStr">
@@ -806,7 +816,6 @@
           <t>ID_20260508113803</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -870,7 +879,6 @@
           <t>ID_20260511071755</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -936,7 +944,6 @@
           <t>ID_20260511074546</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/cuadros/MAYO/GUACARA.xlsx
+++ b/cuadros/MAYO/GUACARA.xlsx
@@ -509,17 +509,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INVERSIONES LA PATRONA 2024, C.A</t>
+          <t>PASTAS CAPRI, C.A.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>420386</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -529,40 +529,40 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>GABRIELA VIVAS</t>
+          <t>YUSBELIS CASTILLO</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
+          <t>DOCUMENTACIÓN ERRÓNEA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>TIPO D</t>
+          <t>TIPO B</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>FALTANTE DE 3KG DE PATILLA</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>1.69</v>
+          <t>SE CARGO AL SISTEMA LA FACTURA DE OTRO PROVEEDOR</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>5379.jpeg</t>
+          <t>SIN_FOTO</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>COBRO</t>
+          <t>NINGUNA</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>HIST_20260504164252</t>
+          <t>ID_20260506083658</t>
         </is>
       </c>
     </row>
@@ -574,17 +574,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LA CARIDAD C.A.</t>
+          <t>RUBROS SANARE C2, C.A.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41793</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -594,40 +594,40 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Robert A. Nuñez</t>
+          <t>Gabriela A. Vivas</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ERROR DE KG EN TARA.</t>
+          <t>DIFERENCIA ENTRE CANTIDAD FISCALIZADA Y DOCUMENTO.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>TIPO C</t>
+          <t>TIPO D</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>diferencia de pesaje por error de tara se colocaron a 2.6kg y las cestas eran 2.3kg, diferencia de 4.6 kg de pollo fresco</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>13.57</v>
+          <t>se cargaron 300gr de mas en el pimenton en sistema eva</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>1.37</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>SIN_FOTO</t>
+          <t>00091910.jpeg</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>RECUPERACIÓN</t>
+          <t>COBRO</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ID_20260505165638</t>
+          <t>ID_20260508113803</t>
         </is>
       </c>
     </row>
@@ -639,17 +639,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PASTAS CAPRI, C.A.</t>
+          <t>PROCESADORA DE VEGETALES Y FRUTAS PROVEFRU, C.A.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>420386</t>
+          <t>20496</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>YUSBELIS CASTILLO</t>
+          <t>ELIANNYS VILLEGAS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SE CARGO AL SISTEMA LA FACTURA DE OTRO PROVEEDOR</t>
+          <t>SE CARGO LA FACTURA EQUIVOCADA</t>
         </is>
       </c>
       <c r="J4" t="n">
@@ -692,7 +692,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>ID_20260506083658</t>
+          <t>ID_20260511071755</t>
         </is>
       </c>
     </row>
@@ -709,12 +709,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>904</t>
+          <t>000001</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -724,22 +724,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Yusbelis C. Montilla</t>
+          <t>NIXILETH V. ARRIZGA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>ERROR DE KG EN TARA.</t>
+          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>TIPO C</t>
+          <t>TIPO A</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>en el melon se cargaron 2 cestas de mas</t>
+          <t>NUMERO DE CONTROL ,Y FACTURRA EQUIVOCADOS</t>
         </is>
       </c>
       <c r="J5" t="n">
@@ -757,7 +757,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>ID_20260508090145</t>
+          <t>ID_20260511074546</t>
         </is>
       </c>
     </row>
@@ -769,17 +769,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RUBROS SANARE C2, C.A.</t>
+          <t>INVERSIONES LA PATRONA 2024, C.A</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>654</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -789,7 +789,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gabriela A. Vivas</t>
+          <t>GABRIELA VIVAS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -804,15 +804,15 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>se cargaron 300gr de mas en el pimenton en sistema eva</t>
+          <t>FALTANTE DE 3KG DE PATILLA YA PAGADO</t>
         </is>
       </c>
       <c r="J6" s="1" t="n">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>00091910.jpeg</t>
+          <t>5379.jpeg</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>ID_20260508113803</t>
+          <t>HIST_20260504164252</t>
         </is>
       </c>
     </row>
@@ -834,17 +834,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>PROCESADORA DE VEGETALES Y FRUTAS PROVEFRU, C.A.</t>
+          <t>LA CARIDAD C.A.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20496</t>
+          <t>41793</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -854,26 +854,26 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ELIANNYS VILLEGAS</t>
+          <t>Robert A. Nuñez</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DOCUMENTACIÓN ERRÓNEA</t>
+          <t>ERROR DE KG EN TARA.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>TIPO B</t>
+          <t>TIPO C</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SE CARGO LA FACTURA EQUIVOCADA</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
+          <t>diferencia de pesaje por error de tara se colocaron a 2.6kg y las cestas eran 2.3kg, diferencia de 4.6 kg de pollo fresco. YA PAGADO</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>13.57</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -882,12 +882,12 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>NINGUNA</t>
+          <t>RECUPERACIÓN</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>ID_20260511071755</t>
+          <t>ID_20260505165638</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>000001</t>
+          <t>904</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -919,22 +919,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>NIXILETH V. ARRIZGA</t>
+          <t>Yusbelis C. Montilla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>NÚMERO DE CONTROL O DOCUMENTO ERRÓNEO.</t>
+          <t>ERROR DE KG EN TARA.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>TIPO A</t>
+          <t>TIPO C</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>NUMERO DE CONTROL ,Y FACTURRA EQUIVOCADOS</t>
+          <t>en el melon se cargaron 2 cestas de mas.</t>
         </is>
       </c>
       <c r="J8" t="n">
@@ -952,7 +952,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>ID_20260511074546</t>
+          <t>ID_20260508090145</t>
         </is>
       </c>
     </row>
